--- a/Sheets/One-Shot Premades/Dinamo.xlsx
+++ b/Sheets/One-Shot Premades/Dinamo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse\Sheets\One-Shot Premades\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Javier\TTRPGs\Marvel Multiverse RPG\Sheets\One-Shot Premades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABC21541-C6DD-4E3B-A1C1-07E5B491B634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E393FA-7E2C-4F23-BD8C-EEBBFA221168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="93">
   <si>
     <t>Defense Score</t>
   </si>
@@ -264,9 +264,6 @@
     <t>Disparo Elemental (Estándar, Instantáneo)</t>
   </si>
   <si>
-    <t>Ataque de Ego vs Defensa de Agilidad a rango normal. En un éxito, daño normal. Si es Fantástico, doble daño y aplica el efecto de tu Elemento.</t>
-  </si>
-  <si>
     <t>Elementos (Permanente)</t>
   </si>
   <si>
@@ -288,31 +285,19 @@
     <t>Dinamo - Arquitecto</t>
   </si>
   <si>
-    <t>+1 Melé  +1 Resiliencia</t>
-  </si>
-  <si>
     <t>Tot. 10</t>
   </si>
   <si>
-    <t>Evasión (Permanente)</t>
-  </si>
-  <si>
     <t>Usas tu Defensa de Agilidad para defenderte contra Ataques de Melé.</t>
   </si>
   <si>
     <t>Resistencia Elemental (Permanente)</t>
   </si>
   <si>
-    <t>Pared Elemental (Estándar, Concentración, 5+ Foco)</t>
-  </si>
-  <si>
     <t>Alzar un Espectáculo</t>
   </si>
   <si>
     <t>Básico</t>
-  </si>
-  <si>
-    <t>Tienes Reducción de Daño de Vida 1 y Reducción de Daño de Foco 1 para cualquier daño que provenga de tu Elemento.</t>
   </si>
   <si>
     <t>Refuerzo Elemental (Reacción)</t>
@@ -342,9 +327,6 @@
     </r>
   </si>
   <si>
-    <t>Protección Elemental (Estándar o Reacción, Instantáneo, 5+ Foco)</t>
-  </si>
-  <si>
     <t>⛭</t>
   </si>
   <si>
@@ -354,10 +336,64 @@
     <t>Conocimiento de Elementos</t>
   </si>
   <si>
-    <t>Disparo Elemental, Resistencia Elemental, Sobrecarga Elemental</t>
-  </si>
-  <si>
-    <t>Volar</t>
+    <t>Tienes un +1 a tu Multiplicador de Daño de Ego.</t>
+  </si>
+  <si>
+    <t>Resiliencia + 1 x 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foco </t>
+  </si>
+  <si>
+    <t>Vigilancia + 1 x 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karma </t>
+  </si>
+  <si>
+    <t>Avances</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10 Puntos por Grado</t>
+  </si>
+  <si>
+    <t>Aguante</t>
+  </si>
+  <si>
+    <t>+5 Avances</t>
+  </si>
+  <si>
+    <t>Ataque de Ego vs Defensa de Agilidad a rango normal. En un éxito, daño normal de Aguante. Si es Fantástico, doble daño y aplica el efecto de tu Elemento.</t>
+  </si>
+  <si>
+    <t>Tienes Reducción de Daño de Aguante 1 y Reducción de Daño de Foco 1 para cualquier daño que provenga de tu Elemento.</t>
+  </si>
+  <si>
+    <t>Cuando eres atacado vs tus Defensas Físicas. Crea una barrera con un Limite de Daño igual al doble del Foco gastado. Mientras mantienes Concentración, el daño que recibes es reducido a 0. Este poder termina si recibes daño mayor o igual al Limite de Daño.</t>
+  </si>
+  <si>
+    <t>Protección Elemental (Estándar o Reacción, Instantáneo, 5 Foco)</t>
+  </si>
+  <si>
+    <t>Disparo Elemental, Resistencia Elemental</t>
+  </si>
+  <si>
+    <t>Evasión (Estandar o Movimiento, Concentracion)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Básico: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Vuelo</t>
+    </r>
   </si>
   <si>
     <r>
@@ -371,55 +407,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Forma Elemental</t>
-    </r>
-  </si>
-  <si>
-    <t>Tienes un +1 a tu Multiplicador de Daño de Ego.</t>
-  </si>
-  <si>
-    <t>Resiliencia + 1 x 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foco </t>
-  </si>
-  <si>
-    <t>Vigilancia + 1 x 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karma </t>
-  </si>
-  <si>
-    <t>Avances</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 10 Puntos por Grado</t>
-  </si>
-  <si>
-    <t>Aguante</t>
-  </si>
-  <si>
-    <t>Al usar un poder de Control Elemental que haga daño, incrementa el daño en 1 por cada 2 Foco gastado.</t>
-  </si>
-  <si>
-    <t>+5 Avances</t>
-  </si>
-  <si>
-    <t>Sobrecarga Elemental (Gratis, Instantáneo, 5+ Foco)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Básico: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Disciplina</t>
+      <t>Sobrecarga Elemental,</t>
     </r>
     <r>
       <rPr>
@@ -430,7 +418,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">, </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
@@ -440,14 +428,26 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Evasión</t>
+      <t>Forma Elemental</t>
     </r>
   </si>
   <si>
-    <t>Cuando eres atacado vs tus Defensas Físicas. Crea una barrera con un Limite de Daño igual al Foco gastado. Mientras mantienes Concentración, el daño que recibes es reducido a 0. Este poder termina si recibes daño mayor o igual al Limite de Daño.</t>
-  </si>
-  <si>
-    <t>Crea una pared de tu Elemento dentro de rango normal, de área igual a hasta 2 por Grado (vertical y horizontalmente). Ataque de Agilidad vs Defensa de Agilidad contra todos los enemigos en el mismo espacio que la pared cuando aparece. En un éxito, elegís en que lado de la pared queda el enemigo. En un fallo, el enemigo elige. Si es Fantástico, aplica el efecto de tu Elemento. La barrera tiene un Limite de Daño igual al Foco gastado + 5. Este poder termina si la pared recibe daño mayor a su Limite de Daño. La pared usa tu Defensa de Ego para sus Defensas Físicas, y es inmune a ataques vs Defensas Mentales.</t>
+    <t>Sobrecarga Elemental (Permanente, 5+ Foco)</t>
+  </si>
+  <si>
+    <t>Al usar un poder de Control Elemental que haga daño, puedes gastar 5 o mas Foco e incrementar el daño en 1 por cada 2 Foco gastado.</t>
+  </si>
+  <si>
+    <t>Disciplina, Evasión</t>
+  </si>
+  <si>
+    <t>Pared Elemental (Estándar, Concentración, Foco igual a Protección Elemental)</t>
+  </si>
+  <si>
+    <t>Crea una pared de tu Elemento dentro de rango normal, de área igual a hasta 2 por Grado (vertical y horizontalmente). Ataque de Agilidad vs Defensa de Agilidad contra todos los enemigos en el mismo espacio que la pared cuando aparece. En un éxito, elegís en que lado de la pared queda el enemigo. En un fallo, el enemigo elige. Si es Fantástico, aplica el efecto de tu Elemento. La barrera tiene un Limite de Daño igual a Protección Elemental. Este poder termina si la pared recibe daño mayor a su Limite de Daño. La pared usa tu Defensa de Ego para sus Defensas Físicas, y es inmune a ataques vs Defensas Mentales.</t>
+  </si>
+  <si>
+    <t>+1 Melé  +1 Vigilancia</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1560,9 +1560,6 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1598,11 +1595,14 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1985,6 +1985,93 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1993,102 +2080,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="44" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="41" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="45" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2558,7 +2549,7 @@
       <c r="H3" s="89"/>
       <c r="I3" s="90"/>
       <c r="K3" s="91" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L3" s="92"/>
       <c r="M3" s="93"/>
@@ -2576,14 +2567,14 @@
       <c r="H4" s="87"/>
       <c r="I4" s="88"/>
       <c r="K4" s="49" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="L4" s="41"/>
       <c r="M4" s="37"/>
     </row>
     <row r="5" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="73" t="s">
-        <v>73</v>
+      <c r="A5" s="72" t="s">
+        <v>67</v>
       </c>
       <c r="B5" s="187" t="s">
         <v>46</v>
@@ -2596,7 +2587,7 @@
       <c r="H5" s="89"/>
       <c r="I5" s="90"/>
       <c r="K5" s="58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L5" s="41"/>
       <c r="M5" s="37"/>
@@ -2668,12 +2659,12 @@
       <c r="M9" s="93"/>
     </row>
     <row r="10" spans="1:22" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="74" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="75"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="76"/>
+      <c r="A10" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="75"/>
       <c r="E10" s="155" t="s">
         <v>31</v>
       </c>
@@ -2689,7 +2680,7 @@
     </row>
     <row r="11" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="100" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="101"/>
@@ -2708,7 +2699,7 @@
       <c r="B12" s="139"/>
       <c r="C12" s="159" t="str">
         <f>_xlfn.CONCAT("/",IF(A32=0,20,20 + A32*IF(Modifiers!O5,Modifiers!O5,20)) + Modifiers!N5)</f>
-        <v>/20</v>
+        <v>/40</v>
       </c>
       <c r="D12" s="160"/>
       <c r="E12" s="31"/>
@@ -2735,12 +2726,12 @@
       <c r="M13" s="93"/>
     </row>
     <row r="14" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="75"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="76"/>
+      <c r="A14" s="73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="74"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="155" t="s">
         <v>31</v>
       </c>
@@ -2754,7 +2745,7 @@
     </row>
     <row r="15" spans="1:22" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="100" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B15" s="101"/>
       <c r="C15" s="101"/>
@@ -2773,7 +2764,7 @@
       <c r="B16" s="139"/>
       <c r="C16" s="159" t="str">
         <f>_xlfn.CONCAT("/",IF(A34=0,20,20 + A34 * IF(Modifiers!O6,Modifiers!O6,20)) + Modifiers!N6)</f>
-        <v>/60</v>
+        <v>/40</v>
       </c>
       <c r="D16" s="160"/>
       <c r="E16" s="31"/>
@@ -2800,11 +2791,11 @@
       <c r="M17" s="93"/>
     </row>
     <row r="18" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="B18" s="75"/>
-      <c r="C18" s="77"/>
+      <c r="A18" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="74"/>
+      <c r="C18" s="76"/>
       <c r="D18" s="157"/>
       <c r="E18" s="155" t="s">
         <v>32</v>
@@ -2842,7 +2833,7 @@
       <c r="D20" s="137"/>
       <c r="E20" s="32" t="str">
         <f>_xlfn.CONCAT("+",IF(Modifiers!K6="Edge",_xlfn.CONCAT(A34,"E"),A34))</f>
-        <v>+2</v>
+        <v>+1</v>
       </c>
       <c r="F20" s="30"/>
       <c r="G20" s="112"/>
@@ -2907,11 +2898,11 @@
       <c r="E24" s="30"/>
       <c r="F24" s="30"/>
       <c r="G24" s="44" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H24" s="45"/>
       <c r="I24" s="39" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J24" s="39"/>
       <c r="K24" s="39"/>
@@ -2966,7 +2957,7 @@
       </c>
       <c r="H27" s="47"/>
       <c r="I27" s="198" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J27" s="198"/>
       <c r="K27" s="198"/>
@@ -2995,7 +2986,7 @@
     </row>
     <row r="29" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="146" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B29" s="147"/>
       <c r="C29" s="148"/>
@@ -3049,13 +3040,13 @@
     </row>
     <row r="32" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" s="126"/>
       <c r="C32" s="127"/>
       <c r="D32" s="131">
         <f xml:space="preserve"> 10 + A32 + Modifiers!B5</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E32" s="132"/>
       <c r="F32" s="30"/>
@@ -3086,13 +3077,13 @@
     </row>
     <row r="34" spans="1:14" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="126"/>
       <c r="C34" s="127"/>
       <c r="D34" s="131">
         <f xml:space="preserve"> 10 + A34 + Modifiers!B6</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="132"/>
       <c r="F34" s="30"/>
@@ -3229,7 +3220,7 @@
     </row>
     <row r="42" spans="1:14" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="164" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B42" s="140" t="e" vm="2">
         <v>#VALUE!</v>
@@ -3323,7 +3314,7 @@
       </c>
       <c r="C46" s="166" t="str">
         <f>_xlfn.CONCAT("X ",IF(Modifiers!G7,Modifiers!G7,$E$8 + Modifiers!F7))</f>
-        <v>X 1</v>
+        <v>X 2</v>
       </c>
       <c r="D46" s="168" t="s">
         <v>7</v>
@@ -3415,16 +3406,16 @@
       <c r="M50" s="37"/>
     </row>
     <row r="51" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="74" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" s="75"/>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="76"/>
+      <c r="A51" s="73" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="74"/>
+      <c r="C51" s="74"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
       <c r="F51" s="30"/>
       <c r="G51" s="46"/>
-      <c r="H51" s="78"/>
+      <c r="H51" s="77"/>
       <c r="I51" s="41"/>
       <c r="J51" s="41"/>
       <c r="K51" s="41"/>
@@ -3433,7 +3424,7 @@
     </row>
     <row r="52" spans="1:13" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="100" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B52" s="101"/>
       <c r="C52" s="101"/>
@@ -3456,7 +3447,7 @@
       </c>
       <c r="D53" s="160"/>
       <c r="E53" s="54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F53" s="30"/>
       <c r="G53" s="184"/>
@@ -3597,27 +3588,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="233" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="237"/>
-      <c r="C1" s="237"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="242" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="243"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="239"/>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="241"/>
+      <c r="A2" s="235"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="212"/>
@@ -3664,19 +3653,19 @@
       <c r="I6" s="220"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="224"/>
-      <c r="B7" s="225"/>
-      <c r="C7" s="225"/>
-      <c r="D7" s="225"/>
-      <c r="E7" s="225"/>
-      <c r="F7" s="225"/>
-      <c r="G7" s="225"/>
-      <c r="H7" s="225"/>
-      <c r="I7" s="226"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="222"/>
+      <c r="C7" s="222"/>
+      <c r="D7" s="222"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
+      <c r="H7" s="222"/>
+      <c r="I7" s="223"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
@@ -3689,120 +3678,120 @@
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="65"/>
+        <v>54</v>
+      </c>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="64"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="66"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="67"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="66"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="221" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="222"/>
-      <c r="C11" s="222"/>
-      <c r="D11" s="222"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="222"/>
-      <c r="I11" s="223"/>
+      <c r="A11" s="215" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="216"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="216"/>
+      <c r="E11" s="216"/>
+      <c r="F11" s="216"/>
+      <c r="G11" s="216"/>
+      <c r="H11" s="216"/>
+      <c r="I11" s="217"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="227" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="228"/>
-      <c r="C12" s="228"/>
-      <c r="D12" s="228"/>
-      <c r="E12" s="228"/>
-      <c r="F12" s="228"/>
-      <c r="G12" s="228"/>
-      <c r="H12" s="228"/>
-      <c r="I12" s="229"/>
+      <c r="A12" s="230" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="231"/>
+      <c r="C12" s="231"/>
+      <c r="D12" s="231"/>
+      <c r="E12" s="231"/>
+      <c r="F12" s="231"/>
+      <c r="G12" s="231"/>
+      <c r="H12" s="231"/>
+      <c r="I12" s="232"/>
     </row>
     <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="215" t="s">
+      <c r="A13" s="227" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="228"/>
+      <c r="C13" s="228"/>
+      <c r="D13" s="228"/>
+      <c r="E13" s="228"/>
+      <c r="F13" s="228"/>
+      <c r="G13" s="228"/>
+      <c r="H13" s="228"/>
+      <c r="I13" s="229"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="230" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="231"/>
+      <c r="C14" s="231"/>
+      <c r="D14" s="231"/>
+      <c r="E14" s="231"/>
+      <c r="F14" s="231"/>
+      <c r="G14" s="231"/>
+      <c r="H14" s="231"/>
+      <c r="I14" s="232"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="215" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="216"/>
-      <c r="C13" s="216"/>
-      <c r="D13" s="216"/>
-      <c r="E13" s="216"/>
-      <c r="F13" s="216"/>
-      <c r="G13" s="216"/>
-      <c r="H13" s="216"/>
-      <c r="I13" s="217"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="206" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="207"/>
-      <c r="C14" s="207"/>
-      <c r="D14" s="207"/>
-      <c r="E14" s="207"/>
-      <c r="F14" s="207"/>
-      <c r="G14" s="207"/>
-      <c r="H14" s="207"/>
-      <c r="I14" s="208"/>
-    </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="209"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
-      <c r="F15" s="210"/>
-      <c r="G15" s="210"/>
-      <c r="H15" s="210"/>
-      <c r="I15" s="211"/>
+      <c r="B15" s="216"/>
+      <c r="C15" s="216"/>
+      <c r="D15" s="216"/>
+      <c r="E15" s="216"/>
+      <c r="F15" s="216"/>
+      <c r="G15" s="216"/>
+      <c r="H15" s="216"/>
+      <c r="I15" s="217"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="215" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="216"/>
-      <c r="C16" s="216"/>
-      <c r="D16" s="216"/>
-      <c r="E16" s="216"/>
-      <c r="F16" s="216"/>
-      <c r="G16" s="216"/>
-      <c r="H16" s="216"/>
-      <c r="I16" s="217"/>
+      <c r="A16" s="206" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="207"/>
+      <c r="C16" s="207"/>
+      <c r="D16" s="207"/>
+      <c r="E16" s="207"/>
+      <c r="F16" s="207"/>
+      <c r="G16" s="207"/>
+      <c r="H16" s="207"/>
+      <c r="I16" s="208"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="233" t="s">
-        <v>87</v>
-      </c>
-      <c r="B17" s="234"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
-      <c r="F17" s="234"/>
-      <c r="G17" s="234"/>
-      <c r="H17" s="234"/>
-      <c r="I17" s="235"/>
+      <c r="A17" s="209"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
+      <c r="D17" s="210"/>
+      <c r="E17" s="210"/>
+      <c r="F17" s="210"/>
+      <c r="G17" s="210"/>
+      <c r="H17" s="210"/>
+      <c r="I17" s="211"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="81" t="s">
-        <v>62</v>
+      <c r="A18" s="79" t="s">
+        <v>59</v>
       </c>
       <c r="B18" s="80"/>
       <c r="C18" s="80"/>
@@ -3811,31 +3800,31 @@
       <c r="F18" s="80"/>
       <c r="G18" s="80"/>
       <c r="H18" s="80"/>
-      <c r="I18" s="79"/>
+      <c r="I18" s="78"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="230" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="231"/>
-      <c r="C19" s="231"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="231"/>
-      <c r="F19" s="231"/>
-      <c r="G19" s="231"/>
-      <c r="H19" s="231"/>
-      <c r="I19" s="232"/>
+      <c r="A19" s="224" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="225"/>
+      <c r="C19" s="225"/>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="225"/>
+      <c r="G19" s="225"/>
+      <c r="H19" s="225"/>
+      <c r="I19" s="226"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="230"/>
-      <c r="B20" s="231"/>
-      <c r="C20" s="231"/>
-      <c r="D20" s="231"/>
-      <c r="E20" s="231"/>
-      <c r="F20" s="231"/>
-      <c r="G20" s="231"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="232"/>
+      <c r="A20" s="224"/>
+      <c r="B20" s="225"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="226"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="212"/>
@@ -4138,20 +4127,20 @@
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A15:I15"/>
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A11:I11"/>
     <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A22:I22"/>
     <mergeCell ref="A23:I23"/>
     <mergeCell ref="A19:I20"/>
-    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A14:I15"/>
+    <mergeCell ref="A16:I17"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A43:I43"/>
@@ -4174,49 +4163,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F52ED7-B55C-4544-B1B9-4049608F227A}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="244" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="245"/>
-      <c r="C1" s="245"/>
-      <c r="D1" s="246"/>
-      <c r="E1" s="242" t="s">
-        <v>88</v>
-      </c>
-      <c r="F1" s="243"/>
+      <c r="A1" s="239" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="245" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="246"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="239" t="s">
+      <c r="A2" s="235" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="241"/>
+      <c r="B2" s="236"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="247" t="s">
+      <c r="A3" s="242" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="248"/>
-      <c r="E3" s="248"/>
-      <c r="F3" s="248"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="248"/>
-      <c r="I3" s="249"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="244"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="215" t="s">
@@ -4233,372 +4222,383 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
+        <v>85</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
       <c r="I5" s="61"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="72"/>
+      <c r="A6" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="70"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="71"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="253" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="254"/>
-      <c r="C7" s="254"/>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="254"/>
-      <c r="G7" s="254"/>
-      <c r="H7" s="254"/>
-      <c r="I7" s="255"/>
+      <c r="A7" s="250" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="251"/>
+      <c r="C7" s="251"/>
+      <c r="D7" s="251"/>
+      <c r="E7" s="251"/>
+      <c r="F7" s="251"/>
+      <c r="G7" s="251"/>
+      <c r="H7" s="251"/>
+      <c r="I7" s="252"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="227" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="228"/>
-      <c r="C8" s="228"/>
-      <c r="D8" s="228"/>
-      <c r="E8" s="228"/>
-      <c r="F8" s="228"/>
-      <c r="G8" s="228"/>
-      <c r="H8" s="228"/>
-      <c r="I8" s="229"/>
+      <c r="A8" s="230" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="231"/>
+      <c r="C8" s="231"/>
+      <c r="D8" s="231"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="231"/>
+      <c r="G8" s="231"/>
+      <c r="H8" s="231"/>
+      <c r="I8" s="232"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="221" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="222"/>
-      <c r="C9" s="222"/>
-      <c r="D9" s="222"/>
-      <c r="E9" s="222"/>
-      <c r="F9" s="222"/>
-      <c r="G9" s="222"/>
-      <c r="H9" s="222"/>
-      <c r="I9" s="223"/>
+      <c r="A9" s="215" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" s="216"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="217"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="230" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="231"/>
-      <c r="C10" s="231"/>
-      <c r="D10" s="231"/>
-      <c r="E10" s="231"/>
-      <c r="F10" s="231"/>
-      <c r="G10" s="231"/>
-      <c r="H10" s="231"/>
-      <c r="I10" s="232"/>
+      <c r="A10" s="256" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="257"/>
+      <c r="C10" s="257"/>
+      <c r="D10" s="257"/>
+      <c r="E10" s="257"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="257"/>
+      <c r="H10" s="257"/>
+      <c r="I10" s="258"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="250" t="s">
-        <v>69</v>
-      </c>
-      <c r="B11" s="251"/>
-      <c r="C11" s="251"/>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="251"/>
-      <c r="G11" s="251"/>
-      <c r="H11" s="251"/>
-      <c r="I11" s="252"/>
+      <c r="A11" s="256"/>
+      <c r="B11" s="257"/>
+      <c r="C11" s="257"/>
+      <c r="D11" s="257"/>
+      <c r="E11" s="257"/>
+      <c r="F11" s="257"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="257"/>
+      <c r="I11" s="258"/>
     </row>
     <row r="12" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="230" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="231"/>
-      <c r="C12" s="231"/>
-      <c r="D12" s="231"/>
-      <c r="E12" s="231"/>
-      <c r="F12" s="231"/>
-      <c r="G12" s="231"/>
-      <c r="H12" s="231"/>
-      <c r="I12" s="232"/>
-    </row>
-    <row r="13" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="256"/>
-      <c r="B13" s="257"/>
-      <c r="C13" s="257"/>
-      <c r="D13" s="257"/>
-      <c r="E13" s="257"/>
-      <c r="F13" s="257"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="257"/>
-      <c r="I13" s="258"/>
-    </row>
-    <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="244" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="245"/>
-      <c r="C15" s="245"/>
-      <c r="D15" s="246"/>
-      <c r="E15" s="242" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="243"/>
-    </row>
-    <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="247" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="249"/>
+    </row>
+    <row r="13" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="224" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="225"/>
+      <c r="C13" s="225"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="226"/>
+    </row>
+    <row r="14" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="253"/>
+      <c r="B14" s="254"/>
+      <c r="C14" s="254"/>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
+      <c r="F14" s="254"/>
+      <c r="G14" s="254"/>
+      <c r="H14" s="254"/>
+      <c r="I14" s="255"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="239" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B16" s="240"/>
       <c r="C16" s="240"/>
-      <c r="D16" s="240"/>
-      <c r="E16" s="240"/>
-      <c r="F16" s="240"/>
-      <c r="G16" s="240"/>
-      <c r="H16" s="240"/>
-      <c r="I16" s="241"/>
+      <c r="D16" s="241"/>
+      <c r="E16" s="245" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="246"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="247" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="248"/>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="249"/>
+      <c r="A17" s="235" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="236"/>
+      <c r="C17" s="236"/>
+      <c r="D17" s="236"/>
+      <c r="E17" s="236"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="236"/>
+      <c r="H17" s="236"/>
+      <c r="I17" s="237"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="221" t="s">
+      <c r="A18" s="242" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="243"/>
+      <c r="C18" s="243"/>
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="244"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="250" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="222"/>
-      <c r="C18" s="222"/>
-      <c r="D18" s="222"/>
-      <c r="E18" s="222"/>
-      <c r="F18" s="222"/>
-      <c r="G18" s="222"/>
-      <c r="H18" s="222"/>
-      <c r="I18" s="223"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="69"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
-      <c r="F19" s="69"/>
-      <c r="G19" s="69"/>
-      <c r="H19" s="69"/>
-      <c r="I19" s="61"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
+      <c r="B19" s="251"/>
+      <c r="C19" s="251"/>
+      <c r="D19" s="251"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="251"/>
+      <c r="G19" s="251"/>
+      <c r="H19" s="251"/>
+      <c r="I19" s="252"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="68"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="68"/>
+      <c r="E20" s="68"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="68"/>
+      <c r="H20" s="68"/>
+      <c r="I20" s="61"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="259" t="s">
+      <c r="A21" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="56"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56"/>
+      <c r="H21" s="56"/>
+      <c r="I21" s="57"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="256" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="257"/>
+      <c r="C22" s="257"/>
+      <c r="D22" s="257"/>
+      <c r="E22" s="257"/>
+      <c r="F22" s="257"/>
+      <c r="G22" s="257"/>
+      <c r="H22" s="257"/>
+      <c r="I22" s="258"/>
+    </row>
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="256"/>
+      <c r="B23" s="257"/>
+      <c r="C23" s="257"/>
+      <c r="D23" s="257"/>
+      <c r="E23" s="257"/>
+      <c r="F23" s="257"/>
+      <c r="G23" s="257"/>
+      <c r="H23" s="257"/>
+      <c r="I23" s="258"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="256"/>
+      <c r="B24" s="257"/>
+      <c r="C24" s="257"/>
+      <c r="D24" s="257"/>
+      <c r="E24" s="257"/>
+      <c r="F24" s="257"/>
+      <c r="G24" s="257"/>
+      <c r="H24" s="257"/>
+      <c r="I24" s="258"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="247" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="248"/>
+      <c r="C25" s="248"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="249"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="224" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="260"/>
-      <c r="C21" s="260"/>
-      <c r="D21" s="260"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="260"/>
-      <c r="G21" s="260"/>
-      <c r="H21" s="260"/>
-      <c r="I21" s="261"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="259"/>
-      <c r="B22" s="260"/>
-      <c r="C22" s="260"/>
-      <c r="D22" s="260"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="260"/>
-      <c r="G22" s="260"/>
-      <c r="H22" s="260"/>
-      <c r="I22" s="261"/>
-    </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="259"/>
-      <c r="B23" s="260"/>
-      <c r="C23" s="260"/>
-      <c r="D23" s="260"/>
-      <c r="E23" s="260"/>
-      <c r="F23" s="260"/>
-      <c r="G23" s="260"/>
-      <c r="H23" s="260"/>
-      <c r="I23" s="261"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="250" t="s">
+      <c r="B26" s="225"/>
+      <c r="C26" s="225"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="226"/>
+    </row>
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="224"/>
+      <c r="B27" s="225"/>
+      <c r="C27" s="225"/>
+      <c r="D27" s="225"/>
+      <c r="E27" s="225"/>
+      <c r="F27" s="225"/>
+      <c r="G27" s="225"/>
+      <c r="H27" s="225"/>
+      <c r="I27" s="226"/>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="224"/>
+      <c r="B28" s="225"/>
+      <c r="C28" s="225"/>
+      <c r="D28" s="225"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="225"/>
+      <c r="G28" s="225"/>
+      <c r="H28" s="225"/>
+      <c r="I28" s="226"/>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="224"/>
+      <c r="B29" s="225"/>
+      <c r="C29" s="225"/>
+      <c r="D29" s="225"/>
+      <c r="E29" s="225"/>
+      <c r="F29" s="225"/>
+      <c r="G29" s="225"/>
+      <c r="H29" s="225"/>
+      <c r="I29" s="226"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="224"/>
+      <c r="B30" s="225"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="226"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="224"/>
+      <c r="B31" s="225"/>
+      <c r="C31" s="225"/>
+      <c r="D31" s="225"/>
+      <c r="E31" s="225"/>
+      <c r="F31" s="225"/>
+      <c r="G31" s="225"/>
+      <c r="H31" s="225"/>
+      <c r="I31" s="226"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="247" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="248"/>
+      <c r="G32" s="248"/>
+      <c r="H32" s="248"/>
+      <c r="I32" s="249"/>
+    </row>
+    <row r="33" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="224" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="251"/>
-      <c r="C24" s="251"/>
-      <c r="D24" s="251"/>
-      <c r="E24" s="251"/>
-      <c r="F24" s="251"/>
-      <c r="G24" s="251"/>
-      <c r="H24" s="251"/>
-      <c r="I24" s="252"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="230" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="231"/>
-      <c r="C25" s="231"/>
-      <c r="D25" s="231"/>
-      <c r="E25" s="231"/>
-      <c r="F25" s="231"/>
-      <c r="G25" s="231"/>
-      <c r="H25" s="231"/>
-      <c r="I25" s="232"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="230"/>
-      <c r="B26" s="231"/>
-      <c r="C26" s="231"/>
-      <c r="D26" s="231"/>
-      <c r="E26" s="231"/>
-      <c r="F26" s="231"/>
-      <c r="G26" s="231"/>
-      <c r="H26" s="231"/>
-      <c r="I26" s="232"/>
-    </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="230"/>
-      <c r="B27" s="231"/>
-      <c r="C27" s="231"/>
-      <c r="D27" s="231"/>
-      <c r="E27" s="231"/>
-      <c r="F27" s="231"/>
-      <c r="G27" s="231"/>
-      <c r="H27" s="231"/>
-      <c r="I27" s="232"/>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="230"/>
-      <c r="B28" s="231"/>
-      <c r="C28" s="231"/>
-      <c r="D28" s="231"/>
-      <c r="E28" s="231"/>
-      <c r="F28" s="231"/>
-      <c r="G28" s="231"/>
-      <c r="H28" s="231"/>
-      <c r="I28" s="232"/>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="230"/>
-      <c r="B29" s="231"/>
-      <c r="C29" s="231"/>
-      <c r="D29" s="231"/>
-      <c r="E29" s="231"/>
-      <c r="F29" s="231"/>
-      <c r="G29" s="231"/>
-      <c r="H29" s="231"/>
-      <c r="I29" s="232"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="230"/>
-      <c r="B30" s="231"/>
-      <c r="C30" s="231"/>
-      <c r="D30" s="231"/>
-      <c r="E30" s="231"/>
-      <c r="F30" s="231"/>
-      <c r="G30" s="231"/>
-      <c r="H30" s="231"/>
-      <c r="I30" s="232"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="250" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="251"/>
-      <c r="C31" s="251"/>
-      <c r="D31" s="251"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="251"/>
-      <c r="G31" s="251"/>
-      <c r="H31" s="251"/>
-      <c r="I31" s="252"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="230" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="231"/>
-      <c r="C32" s="231"/>
-      <c r="D32" s="231"/>
-      <c r="E32" s="231"/>
-      <c r="F32" s="231"/>
-      <c r="G32" s="231"/>
-      <c r="H32" s="231"/>
-      <c r="I32" s="232"/>
-    </row>
-    <row r="33" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="256"/>
-      <c r="B33" s="257"/>
-      <c r="C33" s="257"/>
-      <c r="D33" s="257"/>
-      <c r="E33" s="257"/>
-      <c r="F33" s="257"/>
-      <c r="G33" s="257"/>
-      <c r="H33" s="257"/>
-      <c r="I33" s="258"/>
+      <c r="B33" s="225"/>
+      <c r="C33" s="225"/>
+      <c r="D33" s="225"/>
+      <c r="E33" s="225"/>
+      <c r="F33" s="225"/>
+      <c r="G33" s="225"/>
+      <c r="H33" s="225"/>
+      <c r="I33" s="226"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="253"/>
+      <c r="B34" s="254"/>
+      <c r="C34" s="254"/>
+      <c r="D34" s="254"/>
+      <c r="E34" s="254"/>
+      <c r="F34" s="254"/>
+      <c r="G34" s="254"/>
+      <c r="H34" s="254"/>
+      <c r="I34" s="255"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A32:I33"/>
-    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:I34"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A21:I23"/>
-    <mergeCell ref="A25:I30"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A22:I24"/>
+    <mergeCell ref="A26:I31"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A13:I14"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A10:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A12:I13"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A10:I10"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4629,18 +4629,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="263" t="s">
+      <c r="A1" s="260" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="265"/>
-      <c r="E1" s="263" t="s">
+      <c r="B1" s="261"/>
+      <c r="C1" s="262"/>
+      <c r="E1" s="260" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="264"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
+      <c r="F1" s="261"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="259"/>
+      <c r="I1" s="259"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4681,10 +4681,10 @@
       <c r="G3" s="12">
         <v>0</v>
       </c>
-      <c r="N3" s="267" t="s">
+      <c r="N3" s="264" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="265" t="s">
+      <c r="O3" s="262" t="s">
         <v>15</v>
       </c>
     </row>
@@ -4708,8 +4708,8 @@
         <v>0</v>
       </c>
       <c r="M4" s="27"/>
-      <c r="N4" s="268"/>
-      <c r="O4" s="266"/>
+      <c r="N4" s="265"/>
+      <c r="O4" s="263"/>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -4786,7 +4786,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
